--- a/data/trans_orig/IBSE_100-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IBSE_100-Edad-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,53</t>
+          <t>87,65</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>82,47</t>
+          <t>82,16</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85,29</t>
+          <t>85,04</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,27; 89,52</t>
+          <t>85,75; 89,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,58; 84,87</t>
+          <t>79,09; 84,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,54; 86,79</t>
+          <t>83,42; 86,65</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81,57</t>
+          <t>81,4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80,81</t>
+          <t>79,98</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,15</t>
+          <t>80,67</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,79; 83,54</t>
+          <t>79,51; 83,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,08; 82,47</t>
+          <t>78,42; 81,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,88; 82,41</t>
+          <t>79,41; 81,89</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80,72</t>
+          <t>80,42</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79,1</t>
+          <t>78,83</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79,91</t>
+          <t>79,62</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,03; 82,3</t>
+          <t>78,68; 81,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,92; 80,21</t>
+          <t>77,66; 79,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,93; 80,87</t>
+          <t>78,66; 80,58</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>80,29</t>
+          <t>77,45</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,77</t>
+          <t>74,74</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,84</t>
+          <t>76,06</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76,83; 84,31</t>
+          <t>76,03; 78,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,69; 75,86</t>
+          <t>73,69; 75,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,66; 81,63</t>
+          <t>75,14; 76,86</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73,47</t>
+          <t>73,59</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69,93</t>
+          <t>70,07</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71,73</t>
+          <t>71,84</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,08; 74,97</t>
+          <t>72,06; 75,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,64; 71,24</t>
+          <t>68,78; 71,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,72; 72,73</t>
+          <t>70,89; 72,85</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>74,34</t>
+          <t>74,59</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73,73</t>
+          <t>70,01</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73,96</t>
+          <t>72,21</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72,91; 75,98</t>
+          <t>73,24; 76,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,61; 78,09</t>
+          <t>68,58; 71,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,73; 77,72</t>
+          <t>71,07; 73,09</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>69,33</t>
+          <t>69,5</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>61,68</t>
+          <t>61,76</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64,74</t>
+          <t>64,87</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>67,45; 70,95</t>
+          <t>67,72; 71,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60,31; 62,98</t>
+          <t>60,44; 63,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,66; 65,85</t>
+          <t>63,79; 66,16</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>78,74</t>
+          <t>78,01</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>74,56</t>
+          <t>73,98</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76,6</t>
+          <t>75,94</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,71; 80,8</t>
+          <t>77,33; 78,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,81; 75,62</t>
+          <t>73,45; 74,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75,91; 78,06</t>
+          <t>75,47; 76,37</t>
         </is>
       </c>
     </row>
